--- a/backend/imagenes/Puerto Vallarta Jalisco/1/Formato Puerto Vallarta.xlsx
+++ b/backend/imagenes/Puerto Vallarta Jalisco/1/Formato Puerto Vallarta.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
   <si>
     <t>Ciudad</t>
   </si>
@@ -98,6 +98,21 @@
   </si>
   <si>
     <t xml:space="preserve"> alberca,cine,gym,jacuzzi,salon de fiestas, AC, terraza, rooftop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Vallarta </t>
+  </si>
+  <si>
+    <t>Atún 113, Las Gaviotas, 49328 Puerto Vallarta, Jal.</t>
+  </si>
+  <si>
+    <t>alberca,jacuzzi,AC,jardin,terraza, patio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alberca,gym,jacuzzi,salon de fiestas, terraza, AC, </t>
+  </si>
+  <si>
+    <t>negociable</t>
   </si>
 </sst>
 </file>
@@ -646,7 +661,7 @@
         <v>26</v>
       </c>
       <c r="C9" s="1">
-        <v>80000.0</v>
+        <v>81000.0</v>
       </c>
       <c r="D9" s="1">
         <v>4.0</v>
@@ -671,6 +686,111 @@
       </c>
       <c r="K9" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46000.0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="1">
+        <v>550.0</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1">
+        <v>68000.0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="1">
+        <v>185.0</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1">
+        <v>53000.0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="1">
+        <v>130.0</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/backend/imagenes/Puerto Vallarta Jalisco/1/Formato Puerto Vallarta.xlsx
+++ b/backend/imagenes/Puerto Vallarta Jalisco/1/Formato Puerto Vallarta.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="49">
   <si>
     <t>Ciudad</t>
   </si>
@@ -109,10 +109,55 @@
     <t>alberca,jacuzzi,AC,jardin,terraza, patio</t>
   </si>
   <si>
-    <t xml:space="preserve">alberca,gym,jacuzzi,salon de fiestas, terraza, AC, </t>
+    <t>alberca,gym,jacuzzi,salon de fiestas, terraza, AC, sauna, loungue, jardin, co working, biblioteca , pool table, poker room</t>
   </si>
   <si>
     <t>negociable</t>
+  </si>
+  <si>
+    <t>Av. Francisco Medina Ascencio 2870, Palmar de Aramara, 48314 Puerto Vallarta, Jal.</t>
+  </si>
+  <si>
+    <t>alberca,bodega,AC</t>
+  </si>
+  <si>
+    <t>Av Paseo de la Marina 625, Marina Vallarta, 48335 Puerto Vallarta, Jal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alberca,gym,cancha de tenis, AC, </t>
+  </si>
+  <si>
+    <t>Condomunious Puerto Iguana 187, Isla Iguana, 48333 Puerto Vallarta, Jal.</t>
+  </si>
+  <si>
+    <t>jardin, terraza,patio, AC,bodega, calefaccion alberca,</t>
+  </si>
+  <si>
+    <t>Basilio Badillo 475, Zona Romántica, Emiliano Zapata, 48380 Puerto Vallarta, Jal.</t>
+  </si>
+  <si>
+    <t>terraza, alberca,gym, AC</t>
+  </si>
+  <si>
+    <t>C. Politécnico Nacional 89-int 805, Educación, 48338 Puerto Vallarta, Jal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">terraza,AC,alberca, gym, salon de fiestas </t>
+  </si>
+  <si>
+    <t>2477, Zona Hotelera, Las Glorias, 48300 Puerto Vallarta, Jal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jardin,terraza,AC, bodega, alberca, gym, cine, salon de fiestas, ludoteca </t>
+  </si>
+  <si>
+    <t>María Montessori 360, Zona Hotelera, Zona Hotelera Nte., 48333 Puerto Vallarta, Jal.</t>
+  </si>
+  <si>
+    <t>roof garden, terraza, AC, alberca, gym, jacuzzi,</t>
+  </si>
+  <si>
+    <t>penthouse alberca,gym,jacuzzi,salon de fiestas, terraza, AC, sauna, loungue, jardin, co working, biblioteca , pool table, poker room</t>
   </si>
 </sst>
 </file>
@@ -793,6 +838,388 @@
         <v>33</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1">
+        <v>55000.0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="1">
+        <v>114.0</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1">
+        <v>41000.0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="1">
+        <v>156.0</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="1">
+        <v>79000.0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="1">
+        <v>214.0</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1">
+        <v>60000.0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="1">
+        <v>120.0</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1">
+        <v>48000.0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="1">
+        <v>160.0</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1">
+        <v>85000.0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="1">
+        <v>480.0</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="1">
+        <v>44000.0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" s="1">
+        <v>114.0</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1">
+        <v>58000.0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="1">
+        <v>171.0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="1">
+        <v>80000.0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="1">
+        <v>215.0</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="1">
+        <v>53000.0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="1">
+        <v>120.0</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>82000.0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" s="1">
+        <v>293.0</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
